--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N56_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N56_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.51680720767855</v>
+        <v>8.208981171247766</v>
       </c>
       <c r="D2" t="n">
-        <v>45.11535497217081</v>
+        <v>7.331245182977757</v>
       </c>
       <c r="E2" t="n">
-        <v>17.33541102326468</v>
+        <v>2.817004291280511</v>
       </c>
       <c r="F2" t="n">
-        <v>13.3979666926295</v>
+        <v>2.177169587552294</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.75849079879386</v>
+        <v>8.573254754804003</v>
       </c>
       <c r="D3" t="n">
-        <v>14.98366691062771</v>
+        <v>2.434845872977003</v>
       </c>
       <c r="E3" t="n">
-        <v>17.33541102326468</v>
+        <v>2.817004291280511</v>
       </c>
       <c r="F3" t="n">
-        <v>13.3979666926295</v>
+        <v>2.177169587552294</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.3844133827773</v>
+        <v>6.724967174701312</v>
       </c>
       <c r="D4" t="n">
-        <v>40.57759351298724</v>
+        <v>6.593858945860426</v>
       </c>
       <c r="E4" t="n">
-        <v>17.33541102326468</v>
+        <v>2.817004291280511</v>
       </c>
       <c r="F4" t="n">
-        <v>13.3979666926295</v>
+        <v>2.177169587552294</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.85131921813609</v>
+        <v>6.150839372947115</v>
       </c>
       <c r="D5" t="n">
-        <v>30.681106743263</v>
+        <v>4.985679845780238</v>
       </c>
       <c r="E5" t="n">
-        <v>17.33541102326468</v>
+        <v>2.817004291280511</v>
       </c>
       <c r="F5" t="n">
-        <v>13.3979666926295</v>
+        <v>2.177169587552294</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>79.35077653599795</v>
+        <v>12.89450118709967</v>
       </c>
       <c r="D6" t="n">
-        <v>48.7896336346891</v>
+        <v>7.928315465636979</v>
       </c>
       <c r="E6" t="n">
-        <v>17.33541102326468</v>
+        <v>2.817004291280511</v>
       </c>
       <c r="F6" t="n">
-        <v>13.3979666926295</v>
+        <v>2.177169587552294</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.94923169489336</v>
+        <v>5.679250150420172</v>
       </c>
       <c r="D7" t="n">
-        <v>18.91372527562871</v>
+        <v>3.073480357289665</v>
       </c>
       <c r="E7" t="n">
-        <v>17.33541102326468</v>
+        <v>2.817004291280511</v>
       </c>
       <c r="F7" t="n">
-        <v>13.3979666926295</v>
+        <v>2.177169587552294</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>31.92082214676059</v>
+        <v>5.187133598848596</v>
       </c>
       <c r="D8" t="n">
-        <v>32.53294062653438</v>
+        <v>5.286602851811836</v>
       </c>
       <c r="E8" t="n">
-        <v>17.33541102326468</v>
+        <v>2.817004291280511</v>
       </c>
       <c r="F8" t="n">
-        <v>13.3979666926295</v>
+        <v>2.177169587552294</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>14.21912471695799</v>
+        <v>2.310607766505674</v>
       </c>
       <c r="D9" t="n">
-        <v>14.73065958959608</v>
+        <v>2.393732183309363</v>
       </c>
       <c r="E9" t="n">
-        <v>17.33541102326468</v>
+        <v>2.817004291280511</v>
       </c>
       <c r="F9" t="n">
-        <v>13.3979666926295</v>
+        <v>2.177169587552294</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>5.060328133137933</v>
+        <v>0.8223033216349142</v>
       </c>
       <c r="D10" t="n">
-        <v>4.882814895734756</v>
+        <v>0.7934574205568979</v>
       </c>
       <c r="E10" t="n">
-        <v>17.33541102326468</v>
+        <v>2.817004291280511</v>
       </c>
       <c r="F10" t="n">
-        <v>13.3979666926295</v>
+        <v>2.177169587552294</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>24.23304449868102</v>
+        <v>3.937869731035667</v>
       </c>
       <c r="D11" t="n">
-        <v>23.72127844958127</v>
+        <v>3.854707748056957</v>
       </c>
       <c r="E11" t="n">
-        <v>17.33541102326468</v>
+        <v>2.817004291280511</v>
       </c>
       <c r="F11" t="n">
-        <v>13.3979666926295</v>
+        <v>2.177169587552294</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>51.66836466525497</v>
+        <v>8.396109258103932</v>
       </c>
       <c r="D12" t="n">
-        <v>51.07640698325172</v>
+        <v>8.299916134778403</v>
       </c>
       <c r="E12" t="n">
-        <v>17.33541102326468</v>
+        <v>2.817004291280511</v>
       </c>
       <c r="F12" t="n">
-        <v>13.3979666926295</v>
+        <v>2.177169587552294</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>37.86047844307956</v>
+        <v>6.152327747000429</v>
       </c>
       <c r="D13" t="n">
-        <v>37.40059327592539</v>
+        <v>6.077596407337876</v>
       </c>
       <c r="E13" t="n">
-        <v>17.33541102326468</v>
+        <v>2.817004291280511</v>
       </c>
       <c r="F13" t="n">
-        <v>13.3979666926295</v>
+        <v>2.177169587552294</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>31.81872640837613</v>
+        <v>5.170543041361122</v>
       </c>
       <c r="D14" t="n">
-        <v>32.19765095522826</v>
+        <v>5.232118280224592</v>
       </c>
       <c r="E14" t="n">
-        <v>17.33541102326468</v>
+        <v>2.817004291280511</v>
       </c>
       <c r="F14" t="n">
-        <v>13.3979666926295</v>
+        <v>2.177169587552294</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>37.9894291326258</v>
+        <v>6.173282234051693</v>
       </c>
       <c r="D15" t="n">
-        <v>38.43891500322749</v>
+        <v>6.246323688024468</v>
       </c>
       <c r="E15" t="n">
-        <v>17.33541102326468</v>
+        <v>2.817004291280511</v>
       </c>
       <c r="F15" t="n">
-        <v>13.3979666926295</v>
+        <v>2.177169587552294</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
